--- a/artfynd/A 58690-2024 artfynd.xlsx
+++ b/artfynd/A 58690-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430425</v>
+        <v>121430829</v>
       </c>
       <c r="B4" t="n">
-        <v>98073</v>
+        <v>98015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488707</v>
+        <v>488718</v>
       </c>
       <c r="R4" t="n">
-        <v>6649675</v>
+        <v>6649679</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430829</v>
+        <v>121430425</v>
       </c>
       <c r="B5" t="n">
-        <v>98015</v>
+        <v>98073</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488718</v>
+        <v>488707</v>
       </c>
       <c r="R5" t="n">
-        <v>6649679</v>
+        <v>6649675</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 58690-2024 artfynd.xlsx
+++ b/artfynd/A 58690-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430829</v>
+        <v>121430425</v>
       </c>
       <c r="B4" t="n">
-        <v>98015</v>
+        <v>98073</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219797</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488718</v>
+        <v>488707</v>
       </c>
       <c r="R4" t="n">
-        <v>6649679</v>
+        <v>6649675</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430425</v>
+        <v>121430829</v>
       </c>
       <c r="B5" t="n">
-        <v>98073</v>
+        <v>98015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488707</v>
+        <v>488718</v>
       </c>
       <c r="R5" t="n">
-        <v>6649675</v>
+        <v>6649679</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 58690-2024 artfynd.xlsx
+++ b/artfynd/A 58690-2024 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>121430425</v>
       </c>
       <c r="B4" t="n">
-        <v>98073</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430829</v>
+        <v>121430238</v>
       </c>
       <c r="B5" t="n">
-        <v>98015</v>
+        <v>98127</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Älvhöjden, Vstm</t>
+          <t>Stora Kumlan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488718</v>
+        <v>488727</v>
       </c>
       <c r="R5" t="n">
-        <v>6649679</v>
+        <v>6649672</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430238</v>
+        <v>121430829</v>
       </c>
       <c r="B6" t="n">
-        <v>98121</v>
+        <v>98021</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,34 +1137,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Kumlan, Vstm</t>
+          <t>Östra Älvhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488727</v>
+        <v>488718</v>
       </c>
       <c r="R6" t="n">
-        <v>6649672</v>
+        <v>6649679</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 58690-2024 artfynd.xlsx
+++ b/artfynd/A 58690-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430425</v>
+        <v>121430238</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>98128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,34 +933,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Älvhöjden, Vstm</t>
+          <t>Stora Kumlan, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488707</v>
+        <v>488727</v>
       </c>
       <c r="R4" t="n">
-        <v>6649675</v>
+        <v>6649672</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430238</v>
+        <v>121430425</v>
       </c>
       <c r="B5" t="n">
-        <v>98127</v>
+        <v>98080</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Kumlan, Vstm</t>
+          <t>Östra Älvhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488727</v>
+        <v>488707</v>
       </c>
       <c r="R5" t="n">
-        <v>6649672</v>
+        <v>6649675</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,7 +1124,7 @@
         <v>121430829</v>
       </c>
       <c r="B6" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 58690-2024 artfynd.xlsx
+++ b/artfynd/A 58690-2024 artfynd.xlsx
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430425</v>
+        <v>121430829</v>
       </c>
       <c r="B5" t="n">
-        <v>98080</v>
+        <v>98022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488707</v>
+        <v>488718</v>
       </c>
       <c r="R5" t="n">
-        <v>6649675</v>
+        <v>6649679</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430829</v>
+        <v>121430425</v>
       </c>
       <c r="B6" t="n">
-        <v>98022</v>
+        <v>98080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488718</v>
+        <v>488707</v>
       </c>
       <c r="R6" t="n">
-        <v>6649679</v>
+        <v>6649675</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 58690-2024 artfynd.xlsx
+++ b/artfynd/A 58690-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430238</v>
+        <v>121430829</v>
       </c>
       <c r="B4" t="n">
-        <v>98128</v>
+        <v>98022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,34 +933,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Kumlan, Vstm</t>
+          <t>Östra Älvhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488727</v>
+        <v>488718</v>
       </c>
       <c r="R4" t="n">
-        <v>6649672</v>
+        <v>6649679</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430829</v>
+        <v>121430425</v>
       </c>
       <c r="B5" t="n">
-        <v>98022</v>
+        <v>98080</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488718</v>
+        <v>488707</v>
       </c>
       <c r="R5" t="n">
-        <v>6649679</v>
+        <v>6649675</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430425</v>
+        <v>121430238</v>
       </c>
       <c r="B6" t="n">
-        <v>98080</v>
+        <v>98128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,34 +1137,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219797</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Älvhöjden, Vstm</t>
+          <t>Stora Kumlan, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488707</v>
+        <v>488727</v>
       </c>
       <c r="R6" t="n">
-        <v>6649675</v>
+        <v>6649672</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 58690-2024 artfynd.xlsx
+++ b/artfynd/A 58690-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430829</v>
+        <v>121430425</v>
       </c>
       <c r="B4" t="n">
-        <v>98022</v>
+        <v>98080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219797</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488718</v>
+        <v>488707</v>
       </c>
       <c r="R4" t="n">
-        <v>6649679</v>
+        <v>6649675</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430425</v>
+        <v>121430829</v>
       </c>
       <c r="B5" t="n">
-        <v>98080</v>
+        <v>98022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488707</v>
+        <v>488718</v>
       </c>
       <c r="R5" t="n">
-        <v>6649675</v>
+        <v>6649679</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 58690-2024 artfynd.xlsx
+++ b/artfynd/A 58690-2024 artfynd.xlsx
@@ -1012,17 +1012,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430425</v>
+        <v>121430238</v>
       </c>
       <c r="B5" t="n">
-        <v>98088</v>
+        <v>98136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Älvhöjden, Vstm</t>
+          <t>Stora Kumlan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488707</v>
+        <v>488727</v>
       </c>
       <c r="R5" t="n">
-        <v>6649675</v>
+        <v>6649672</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430238</v>
+        <v>121430425</v>
       </c>
       <c r="B6" t="n">
-        <v>98136</v>
+        <v>98088</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,34 +1137,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Kumlan, Vstm</t>
+          <t>Östra Älvhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488727</v>
+        <v>488707</v>
       </c>
       <c r="R6" t="n">
-        <v>6649672</v>
+        <v>6649675</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
